--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,31 +494,31 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -851,10 +851,8 @@
           <t>Ranjana Yadav</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9819622436</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9819622436</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9844495200</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9844495200</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.656123</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.656123</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,50 +942,659 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.339142</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.339142</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>6d 23h</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 9:14 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357638</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Hari Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Hari Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9745942422</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:19:39 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>LTP9745942422</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:57:58 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:14:14 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Shanta bhawan Shanta bhawan - Bicycle store M8J4+36M ????? ??? Lalitpur 44600, Lalitpur, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9745942422@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB222</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 54m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 16m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 9:21 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359234</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841367090</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9841367090</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:58:54 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.6851</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near to Guna Airlines Pvt. Ltd. , Aaloknagar , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ramthuldai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>04:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.33957</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 22m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 9:18 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357447</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Prasad Joshi</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Prasad Joshi</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851342295</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851342295</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:36:39 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank (NIMB) M8JJ+67V, Shankhamul Brg, Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>06:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 41m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1006,13 +1609,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -1043,7 +1646,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1053,7 +1656,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1064,7 +1667,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1691,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>6d 23h</t>
+          <t>4d 14h 41m</t>
         </is>
       </c>
     </row>
@@ -1125,218 +1728,434 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TKT1353630</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Ranjana Yadav</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>6d 23h</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359234</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:58:54 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2d 21h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357447</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Prasad Joshi</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:36:39 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,12 +512,12 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1052,10 +1052,8 @@
           <t>Hari Bahadur Bhujel</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9745942422</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9745942422</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1141,10 +1139,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1155,7 +1151,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1251,10 +1247,8 @@
           <t>Ram Sharan Khatri</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841367090</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841367090</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1289,10 +1283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.6851</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.6851</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1348,25 +1340,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33957</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33956999999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1462,10 +1450,8 @@
           <t>Birendra Prasad Joshi</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851342295</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851342295</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1555,10 +1541,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1569,32 +1553,243 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 41m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>6g router khoi..</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361092</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Raut</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Raut</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9844360431</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9844360431</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:25:13 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.67071</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>I J Pioneer School - Higher secondary school J8WP+F6J Lalitpur 44700, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>siddhartharaut33@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>11:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB522</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.32264</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>3d 23h 41m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 22m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1646,7 +1841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1656,7 +1851,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1667,7 +1862,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1886,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4d 14h 41m</t>
+          <t>3d 20h 51m</t>
         </is>
       </c>
     </row>
@@ -1750,10 +1945,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1849,10 +2044,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2058,7 +2253,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2125,14 +2320,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:18:19 AM</t>
@@ -2156,6 +2351,73 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>3d 23h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361092</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Siddhartha Raut</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:25:13 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1649,10 +1649,8 @@
           <t>Siddhartha Raut</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9844360431</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9844360431</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1687,10 +1685,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.67071</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.67071</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1746,25 +1742,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB522</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.32264</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.32264000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1813,7 +1805,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2387,7 +2379,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1780,6 +1780,205 @@
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359263</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Anju Dahal</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Anju Dahal</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9807023527</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:49 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9807023527</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:15:32 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:49 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Sagarmatha Engineering College, M8Q3+729, Lalitpur 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>dahalanju043@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L59-6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 48m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1833,7 +2032,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1854,7 +2053,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1937,14 +2136,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2036,14 +2235,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1852,10 +1852,8 @@
           <t>Anju Dahal</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9807023527</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9807023527</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1941,10 +1939,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1955,30 +1951,452 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 48m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>2d 21h 48m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>remote damage</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362893</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9745611801</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:11:00 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841750424</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:58:24 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24:57 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.676553</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur  ward no:3,Pulchowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>hjackdec25@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.315742</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:22 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>remote damage</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362893</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9745611801</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:11:00 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841750424</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:58:24 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24:57 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.676553</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur  ward no:3,Pulchowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>hjackdec25@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>00:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.315742</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1995,16 +2413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2032,7 +2450,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2042,7 +2460,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2053,7 +2471,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2483,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>24m</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2495,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 20h 51m</t>
+          <t>2d 14h 23m</t>
         </is>
       </c>
     </row>
@@ -2150,343 +2568,250 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1359234</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Ram Sharan Khatri</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2516,22 +2841,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2541,74 +2866,342 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>TKT1359234</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:58:54 AM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:21:21 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2d 21h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357447</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Prasad Joshi</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:36:39 AM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:18:19 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1361092</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Siddhartha Raut</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>1d 15h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362893</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:11:00 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:58:24 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24:57 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362893</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:11:00 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:58:24 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24:57 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,7 +527,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -2047,10 +2047,8 @@
           <t>Sushila Shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9745611801</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9745611801</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2085,10 +2083,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.676553</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.676553</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2144,25 +2140,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.315742</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.315742</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2258,10 +2250,8 @@
           <t>Sushila Shrestha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9745611801</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9745611801</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2296,10 +2286,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.676553</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.676553</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2355,50 +2343,1085 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.315742</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.315742</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>1h 13m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>1h 26m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:44 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Slow issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357830</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9823142863</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:17 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>CHB9823142863</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:29:40 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:44:17 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.69629624635759</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>ktm new road indrachowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>dtf5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Tika Kathayat</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB392</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32497406005861</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 7m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 14m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Slow issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357830</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9823142863</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:17 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CHB9823142863</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:29:40 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:44:17 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.69629624635759</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>ktm new road indrachowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>dtf5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>06:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Tika Kathayat</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB392</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.32497406005861</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 7m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 14m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade WIFI6 Router</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360911</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9862103678</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:08:22 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>abishek_fttx</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:07:29 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:41:39 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.697095</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Mini Land Secondary School, M8X4+27J, ????? ?????, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>gaminghubytnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB327</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.306179</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 33m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 34m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359155</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Ranjita Pandey</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Ranjita Pandey</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9860495234</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36:48 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>LTP9860495234</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:21:29 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36:48 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Chakupati near sankhamul, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>05:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 15m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362055</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.68556</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Sanepa Meat Shop Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>kapilshahi885@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.30718</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>19h 53m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>19h 53m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2413,7 +3436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2450,7 +3473,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2460,7 +3483,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2471,7 +3494,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +3506,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>24m</t>
+          <t>21h 11m</t>
         </is>
       </c>
     </row>
@@ -2495,7 +3518,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 14h 23m</t>
+          <t>2d 22h 27m</t>
         </is>
       </c>
     </row>
@@ -2554,14 +3577,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2601,351 +3624,258 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1359234</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Ram Sharan Khatri</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>2d 21h 22m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2975,22 +3905,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3000,29 +3930,29 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3042,22 +3972,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3067,141 +3997,476 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1361092</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Siddhartha Raut</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:25:13 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:47:39 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 15h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1362893</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Sushila Shrestha</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:11:00 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:58:24 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:24:57 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362893</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Sushila Shrestha</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>1h 13m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>1h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357830</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:17 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:29:40 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:44:17 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 7m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357830</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:17 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:29:40 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:44:17 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>3d 22h 7m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>3d 22h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359155</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Ranjita Pandey</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36:48 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:21:29 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:36:48 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2453,10 +2453,8 @@
           <t>Gitaraj B.K</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9823142863</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9823142863</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2491,10 +2489,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.69629624635759</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.69629624635759</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2550,25 +2546,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>CDB392</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32497406005861</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32497406005861</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2664,10 +2656,8 @@
           <t>Gitaraj B.K</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9823142863</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9823142863</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2702,10 +2692,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.69629624635759</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.69629624635759</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2761,25 +2749,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>CDB392</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.32497406005861</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.32497406005861</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2875,10 +2859,8 @@
           <t>Abishek Chaudhary</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9862103678</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9862103678</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2913,10 +2895,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.697095</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.697095</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2968,25 +2948,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB327</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.306179</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.306179</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3082,10 +3058,8 @@
           <t>Ranjita Pandey</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9860495234</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9860495234</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3175,10 +3149,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3189,7 +3161,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3285,10 +3257,8 @@
           <t>Ravi Shahi</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851071622</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851071622</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3323,10 +3293,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.68556</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.68556</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3378,25 +3346,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.30718</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.30718</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3445,7 +3409,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4302,7 +4266,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4369,7 +4333,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4436,7 +4400,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3384,6 +3384,428 @@
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade WIFI6 Router</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360911</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9862103678</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>abishek_fttx</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:07:29 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.697095</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Mini Land Secondary School, M8X4+27J, ????? ?????, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>gaminghubytnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>15:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB327</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.306179</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 7m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360598</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851185086</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>santoshshrestha</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:10:30 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.67664</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Pulchowk Pimbahal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>santoshshr@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>18:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.32135</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3400,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3409,7 +3831,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3437,7 +3859,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3447,7 +3869,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3458,7 +3880,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3892,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21h 11m</t>
+          <t>17h 20m</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3904,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 27m</t>
+          <t>2d 17h 45m</t>
         </is>
       </c>
     </row>
@@ -3541,14 +3963,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3676,14 +4098,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4431,6 +4853,140 @@
       <c r="M34" s="3" t="inlineStr">
         <is>
           <t>2d 23h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360911</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:07:29 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1d 19h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360598</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:10:30 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3456,10 +3456,8 @@
           <t>Abishek Chaudhary</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9862103678</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9862103678</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3494,10 +3492,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.697095</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.697095</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3553,25 +3549,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB327</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.306179</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.306179</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3667,10 +3659,8 @@
           <t>Santosh Shrestha</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851185086</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851185086</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3705,10 +3695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.67664</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67664</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3764,25 +3752,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.32135</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.32135</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3831,7 +3815,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4889,7 +4873,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4956,7 +4940,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3790,6 +3790,428 @@
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:50:53 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37:09 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.75259</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Home Tarkeshwor-5, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>parkasnepal423@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>23:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L62-4</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.2867</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:50:53 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37:09 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.75259</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Home Tarkeshwor-5, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>parkasnepal423@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>23:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L62-4</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.2867</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3806,7 +4228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3815,7 +4237,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3843,7 +4265,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3853,7 +4275,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3864,7 +4286,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -3876,7 +4298,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 20m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
@@ -3888,7 +4310,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 17h 45m</t>
+          <t>3d 5h 24m</t>
         </is>
       </c>
     </row>
@@ -3947,14 +4369,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4082,14 +4504,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4971,6 +5393,140 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:50:53 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37:09 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:50:53 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37:09 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3862,10 +3862,8 @@
           <t>Parkas Nepal</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849025416</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849025416</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3900,10 +3898,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.75259</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.75259</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3959,25 +3955,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L62-4</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.2867</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.2867</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4073,10 +4065,8 @@
           <t>Parkas Nepal</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9849025416</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9849025416</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4111,10 +4101,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.75259</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.75259</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4170,50 +4158,253 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L62-4</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.2867</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.2867</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>2d 46m</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>5d 21h 33m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:59 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355718</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841258917</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:59:14 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>nilambasnet</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:34:53 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:59:14 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.67657</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Dhobighat, near by  Progress Boys Hostel, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>javanbansent71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.30774</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>5d 18h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4428,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4265,7 +4456,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -4286,7 +4477,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -4369,14 +4560,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4504,14 +4695,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5620,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5496,7 +5687,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4268,10 +4268,8 @@
           <t>Nilam Karki Basnet</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841258917</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841258917</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4306,10 +4304,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.67657</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.67657</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4361,50 +4357,1086 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.30774</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.30774</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>5d 18h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr"/>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:08 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="AA22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Setup box  auto off</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358019</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:26:23 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:58:13 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:55:15 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 28m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 57m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360253</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9808583264</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:02:38 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9808583264</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:42:25 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:02:38 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.68819</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Kupondole Near nightingale school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>ajayk.chaudhary85@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>22:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB688</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.31269</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>5d 18h 24m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4419,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4428,7 +5460,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4456,7 +5488,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -4466,7 +5498,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4477,7 +5509,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -4489,7 +5521,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 10m</t>
+          <t>1d 1h 26m</t>
         </is>
       </c>
     </row>
@@ -4501,7 +5533,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 5h 24m</t>
+          <t>3d 4h 42m</t>
         </is>
       </c>
     </row>
@@ -4560,14 +5592,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -4578,10 +5610,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -4625,126 +5657,117 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -4755,311 +5778,171 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1359234</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Ram Sharan Khatri</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>2d 21h 22m</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1357447</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Birendra Prasad Joshi</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>3d 23h 41m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5089,22 +5972,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5114,39 +5997,39 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5156,64 +6039,64 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5223,64 +6106,64 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1361092</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Siddhartha Raut</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -5290,54 +6173,54 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5357,64 +6240,64 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1359155</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Ranjita Pandey</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5424,64 +6307,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:21:29 AM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 15m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1360911</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Abishek Chaudhary</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5491,64 +6374,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:07:29 PM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 7m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1360598</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5558,44 +6441,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:10:30 PM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1355352</t>
+          <t>TKT1359155</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Parkas Nepal</t>
+          <t>Ranjita Pandey</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -5610,12 +6493,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5625,99 +6508,434 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:50:53 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:03:59 PM</t>
+          <t>05 Oct 2026 11:21:29 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:37:09 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2d 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>5d 21h 33m</t>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>TKT1360911</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Chaudhary</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:07:29 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:14:37 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360598</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:10:30 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:16:25 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>TKT1355352</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Parkas Nepal</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 10:50:53 AM</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 02:03:59 PM</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 11:37:09 AM</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>2d 46m</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>5d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:50:53 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:37:09 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>2d 46m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>5d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358019</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:26:23 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:58:13 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:55:15 AM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 28m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360253</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:02:38 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:42:25 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:02:38 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4982,10 +4982,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5020,10 +5018,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5079,25 +5075,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5296,10 +5288,8 @@
           <t>Ajay Kumar Chaudhary</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9808583264</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9808583264</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5334,10 +5324,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.68819</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.68819</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5393,50 +5381,663 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB688</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.31269</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.31269</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360955</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>GAURAV KOIRALA</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>GAURAV KOIRALA</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9865711453</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28:41 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9865711453</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:36:08 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28:41 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.64598</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Satdobato (Inside Ring Road) Dhapakhel near sumeru hospital, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>gauravkoirala88@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>15:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB542</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.32493</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 20m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 52m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW27" s="3" t="inlineStr">
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9741716174</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:10:34 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>CHB9741716174</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28:20 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>New baneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>9741716174@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>2d 17m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 18m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi -6 router</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355547</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Jaisawal</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Jaisawal</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9813575302</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:26:32 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9813575302</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:52:51 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:26:32 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>new baneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>22:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB622</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 33m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -5451,7 +6052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5488,7 +6089,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -5498,7 +6099,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -5509,7 +6110,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +6122,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 26m</t>
+          <t>22h 27m</t>
         </is>
       </c>
     </row>
@@ -5533,7 +6134,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 4h 42m</t>
+          <t>3d 6h 32m</t>
         </is>
       </c>
     </row>
@@ -5592,14 +6193,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -5741,14 +6342,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -6838,7 +7439,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -6905,14 +7506,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 12:02:38 PM</t>
@@ -6936,6 +7537,140 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>2d 2h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360955</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>GAURAV KOIRALA</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28:41 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:36:08 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:28:41 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355547</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Kishan Jaisawal</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:26:32 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:52:51 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:26:32 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>5d 20h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5491,10 +5491,8 @@
           <t>GAURAV KOIRALA</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9865711453</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9865711453</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5529,10 +5527,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.64598</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.64598</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -5588,25 +5584,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>CDB542</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.32493</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.32492999999999</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5702,10 +5694,8 @@
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9741716174</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9741716174</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5777,10 +5767,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr"/>
       <c r="AJ29" s="3" t="inlineStr"/>
@@ -5795,10 +5783,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -5809,7 +5795,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -5905,10 +5891,8 @@
           <t>Kishan Jaisawal</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9813575302</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9813575302</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5998,10 +5982,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6012,32 +5994,231 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 33m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>5d 20h 33m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359719</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Subedi</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Subedi</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9863501683</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:36:18 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>BKT9863501683</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:36:18 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:45:52 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Lokanthali Madhyapur Thimi 44600, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>9863501683@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L7-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 9m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 9m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6242,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6089,7 +6270,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -6110,7 +6291,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -6193,14 +6374,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -6342,14 +6523,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>11</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7754,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7640,7 +7821,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,13 +517,13 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="21" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -6090,10 +6090,8 @@
           <t>Sagar Subedi</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9863501683</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9863501683</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6179,10 +6177,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6193,30 +6189,953 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 9m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 9m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 9m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 9m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360866</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9803014626</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803014626</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:53:09 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Aarambha Montessori Sobha Bhagwati Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>sagarshahi409@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>17:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB202</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360866</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9803014626</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803014626</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:53:09 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Aarambha Montessori Sobha Bhagwati Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>sagarshahi409@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>17:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB202</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:47:57 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.67713</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near by radhe radhe Vatbhatini, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L64-1</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.395276</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 13m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 13m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW31" s="3" t="inlineStr">
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:02 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361710</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Abhisekh chhetri</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Abhisekh chhetri</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9769893390</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9769893390</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:30:38 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.695311</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Near Ar Online Company - Business center Shantinagar OM kareshwor, Kathmandu, 31 Kathmandu 44600, Ba</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>abhisekhchhetri3390@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>11:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>L34-6</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.346982</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6233,7 +7152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6242,7 +7161,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6270,7 +7189,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -6280,7 +7199,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6291,7 +7210,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -6303,7 +7222,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 27m</t>
+          <t>23h 35m</t>
         </is>
       </c>
     </row>
@@ -6315,7 +7234,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 6h 32m</t>
+          <t>3d 32m</t>
         </is>
       </c>
     </row>
@@ -6374,14 +7293,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6523,14 +7442,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7855,6 +8774,207 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360866</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:53:09 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360866</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Sagar Shahi</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:46:11 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:53:09 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361710</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Abhisekh chhetri</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:30:38 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 29m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6285,10 +6285,8 @@
           <t>Krishna Sagar Shahi</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9803014626</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9803014626</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6378,10 +6376,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -6392,7 +6388,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6488,10 +6484,8 @@
           <t>Krishna Sagar Shahi</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9803014626</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9803014626</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6581,10 +6575,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -6595,7 +6587,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6681,20 +6673,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Puspa KC</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6729,10 +6715,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.67713</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.67713</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6780,25 +6764,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>L64-1</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.395276</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.395276</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6997,10 +6977,8 @@
           <t>Abhisekh chhetri</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9769893390</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9769893390</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7035,10 +7013,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.695311</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.695311</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7094,25 +7070,21 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>L34-6</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.346982</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.346982</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7161,7 +7133,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8807,7 +8779,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -8874,7 +8846,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -8941,7 +8913,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7113,6 +7113,217 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:30 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363012</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Raj Amatya</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Raj Amatya</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9813502103</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:30:36 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9813502103</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:14:14 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:30:36 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.66704</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Little Angels' College M83P+7MM, lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>pratikamatya9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB473</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.32456</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7124,7 +7335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7133,7 +7344,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7161,7 +7372,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -7171,7 +7382,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -7182,7 +7393,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7405,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23h 35m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7417,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 32m</t>
+          <t>2d 21h 14m</t>
         </is>
       </c>
     </row>
@@ -7265,14 +7476,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -7414,14 +7625,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -8947,6 +9158,73 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363012</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Pratik Raj Amatya</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:30:36 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:14:14 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:30:36 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -7180,10 +7180,8 @@
           <t>Pratik Raj Amatya</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9813502103</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9813502103</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7218,10 +7216,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.66704</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.66704</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7277,50 +7273,1300 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB473</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.32456</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.32456000000001</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:42 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360491</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Tirtha Kumari Limbu</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Tirtha Kumari Limbu</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9704585986</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9810099369</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:06:26 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.72392</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Bhrikuti Chowk Bus Stop - Bus stop Saraswatinagar Rd 6 Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>21:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L51-5</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.34985</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>3h 16m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 36m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:33:19 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359185</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Parbati Ghale</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Parbati Ghale</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9841022579</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:31:17 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9841022579</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:38:20 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:31:17 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.696636</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near Salik Chowk ParkKalanki, Kathmandu 44600, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>prashanghale60@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB324</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.277157</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:29 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:29:02 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:26 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>stb issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>00:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:25 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>stb issue</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>00:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -7335,13 +8581,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -7372,7 +8618,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -7382,7 +8628,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -7393,7 +8639,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -7405,7 +8651,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>19h 40m</t>
         </is>
       </c>
     </row>
@@ -7417,7 +8663,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 14m</t>
+          <t>2d 14h 40m</t>
         </is>
       </c>
     </row>
@@ -7476,14 +8722,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -7512,10 +8758,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -7625,14 +8871,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -7708,12 +8954,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -7729,181 +8975,137 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1359234</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ram Sharan Khatri</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7923,22 +9125,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -7948,29 +9150,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 22m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7990,22 +9192,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -8015,19 +9217,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8057,22 +9259,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -8082,39 +9284,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1361092</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Siddhartha Raut</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -8124,32 +9326,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>
@@ -8223,22 +9425,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8258,32 +9460,32 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
@@ -8357,32 +9559,32 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1359155</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Ranjita Pandey</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -8392,44 +9594,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:21:29 AM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 23h 15m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1360911</t>
+          <t>TKT1359155</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Abishek Chaudhary</t>
+          <t>Ranjita Pandey</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8459,22 +9661,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:07:29 PM</t>
+          <t>05 Oct 2026 11:21:29 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -8484,19 +9686,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 7m</t>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1360598</t>
+          <t>TKT1360911</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Abishek Chaudhary</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8526,22 +9728,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:10:30 PM</t>
+          <t>06 Oct 2026 04:07:29 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -8551,19 +9753,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>1d 19h 7m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1355352</t>
+          <t>TKT1360598</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Parkas Nepal</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8578,12 +9780,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -8593,32 +9795,32 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:50:53 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:03:59 PM</t>
+          <t>06 Oct 2026 01:10:30 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:37:09 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2d 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>5d 21h 33m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
@@ -8692,22 +9894,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1358019</t>
+          <t>TKT1355352</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Parkas Nepal</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8727,64 +9929,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:26:23 PM</t>
+          <t>06 Oct 2026 10:50:53 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 01:58:13 PM</t>
+          <t>02 Oct 2026 02:03:59 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:55:15 AM</t>
+          <t>08 Oct 2026 11:37:09 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 28m</t>
+          <t>2d 46m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 57m</t>
+          <t>5d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1360253</t>
+          <t>TKT1358019</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Ajay Kumar Chaudhary</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -8794,44 +9996,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>04 Oct 2026 02:26:23 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 09:42:25 AM</t>
+          <t>04 Oct 2026 01:58:13 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>08 Oct 2026 11:55:15 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 21h 28m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 20m</t>
+          <t>3d 21h 57m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1360955</t>
+          <t>TKT1360253</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>GAURAV KOIRALA</t>
+          <t>Ajay Kumar Chaudhary</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8861,22 +10063,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:36:08 PM</t>
+          <t>06 Oct 2026 09:42:25 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -8886,19 +10088,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 52m</t>
+          <t>2d 2h 20m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1355547</t>
+          <t>TKT1360955</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Kishan Jaisawal</t>
+          <t>GAURAV KOIRALA</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8928,22 +10130,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:52:51 PM</t>
+          <t>06 Oct 2026 04:36:08 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -8953,19 +10155,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 33m</t>
+          <t>1d 19h 52m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1360866</t>
+          <t>TKT1355547</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Krishna Sagar Shahi</t>
+          <t>Kishan Jaisawal</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8980,12 +10182,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -8995,32 +10197,32 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>02 Oct 2026 03:52:51 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:53:09 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>5d 20h 33m</t>
         </is>
       </c>
     </row>
@@ -9094,12 +10296,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1361710</t>
+          <t>TKT1360866</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Abhisekh chhetri</t>
+          <t>Krishna Sagar Shahi</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9114,12 +10316,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -9129,99 +10331,367 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:30:38 AM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>08 Oct 2026 12:53:09 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 29m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>TKT1361710</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Abhisekh chhetri</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:30:38 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:08 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>TKT1363012</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Pratik Raj Amatya</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 10:14:14 AM</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360491</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Tirtha Kumari Limbu</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:06:26 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7383,10 +7383,8 @@
           <t>Tirtha Kumari Limbu</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9704585986</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9704585986</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7421,10 +7419,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.72392</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.72392</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7480,25 +7476,21 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>L51-5</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.34985</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.34985</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7594,10 +7586,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7632,10 +7622,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.69354</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.69354</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -7687,25 +7675,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7801,10 +7785,8 @@
           <t>Parbati Ghale</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9841022579</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9841022579</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7839,10 +7821,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.696636</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.696636</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -7894,25 +7874,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>CDB324</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.277157</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.277157</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8008,10 +7984,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8046,10 +8020,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.699563</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.699563</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8101,25 +8073,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8215,10 +8183,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8253,10 +8219,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8312,25 +8276,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8426,10 +8386,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8464,10 +8422,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8523,48 +8479,659 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : stb issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="AA44" s="3" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AC44" s="3" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr"/>
+      <c r="AF44" s="3" t="inlineStr"/>
+      <c r="AG44" s="3" t="inlineStr"/>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr"/>
+      <c r="AN44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr"/>
+      <c r="AA45" s="3" t="inlineStr"/>
+      <c r="AB45" s="3" t="inlineStr"/>
+      <c r="AC45" s="3" t="inlineStr"/>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr"/>
+      <c r="AF45" s="3" t="inlineStr"/>
+      <c r="AG45" s="3" t="inlineStr"/>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr"/>
+      <c r="AN45" s="3" t="inlineStr"/>
+      <c r="AO45" s="3" t="inlineStr"/>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="AA46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:59 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Iptv issue</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360585</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9841213338</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:27:53 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841213338</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:00:36 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:59:40 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Lampati marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>20:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB303</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 31m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 59m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
@@ -8581,7 +9148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8618,7 +9185,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -8628,7 +9195,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -8639,7 +9206,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -8651,7 +9218,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>19h 40m</t>
+          <t>20h 47m</t>
         </is>
       </c>
     </row>
@@ -8663,7 +9230,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 14h 40m</t>
+          <t>2d 14h 7m</t>
         </is>
       </c>
     </row>
@@ -8758,10 +9325,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -8977,19 +9544,19 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -8998,181 +9565,137 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1359234</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Ram Sharan Khatri</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -9192,22 +9715,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -9217,29 +9740,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 22m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -9259,22 +9782,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -9284,19 +9807,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -9326,22 +9849,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -9351,39 +9874,39 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1361092</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Siddhartha Raut</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -9393,32 +9916,32 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>
@@ -9492,22 +10015,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -9527,32 +10050,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
@@ -9626,32 +10149,32 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1359155</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Ranjita Pandey</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -9661,44 +10184,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:21:29 AM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 15m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1360911</t>
+          <t>TKT1359155</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Abishek Chaudhary</t>
+          <t>Ranjita Pandey</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -9728,22 +10251,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:07:29 PM</t>
+          <t>05 Oct 2026 11:21:29 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9753,19 +10276,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 7m</t>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1360598</t>
+          <t>TKT1360911</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Abishek Chaudhary</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9795,22 +10318,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:10:30 PM</t>
+          <t>06 Oct 2026 04:07:29 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -9820,19 +10343,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>1d 19h 7m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1355352</t>
+          <t>TKT1360598</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Parkas Nepal</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9847,12 +10370,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9862,32 +10385,32 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:50:53 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:03:59 PM</t>
+          <t>06 Oct 2026 01:10:30 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:37:09 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2d 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>5d 21h 33m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
@@ -9961,22 +10484,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1358019</t>
+          <t>TKT1355352</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Parkas Nepal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -9996,64 +10519,64 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:26:23 PM</t>
+          <t>06 Oct 2026 10:50:53 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 01:58:13 PM</t>
+          <t>02 Oct 2026 02:03:59 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:55:15 AM</t>
+          <t>08 Oct 2026 11:37:09 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 28m</t>
+          <t>2d 46m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 57m</t>
+          <t>5d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1360253</t>
+          <t>TKT1358019</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ajay Kumar Chaudhary</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -10063,44 +10586,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>04 Oct 2026 02:26:23 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 09:42:25 AM</t>
+          <t>04 Oct 2026 01:58:13 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>08 Oct 2026 11:55:15 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 21h 28m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 20m</t>
+          <t>3d 21h 57m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1360955</t>
+          <t>TKT1360253</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>GAURAV KOIRALA</t>
+          <t>Ajay Kumar Chaudhary</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -10130,22 +10653,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:36:08 PM</t>
+          <t>06 Oct 2026 09:42:25 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -10155,19 +10678,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 52m</t>
+          <t>2d 2h 20m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1355547</t>
+          <t>TKT1360955</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Kishan Jaisawal</t>
+          <t>GAURAV KOIRALA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10197,22 +10720,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:52:51 PM</t>
+          <t>06 Oct 2026 04:36:08 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -10222,19 +10745,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 33m</t>
+          <t>1d 19h 52m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1360866</t>
+          <t>TKT1355547</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Krishna Sagar Shahi</t>
+          <t>Kishan Jaisawal</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -10249,12 +10772,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -10264,32 +10787,32 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>02 Oct 2026 03:52:51 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:53:09 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>5d 20h 33m</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10886,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1361710</t>
+          <t>TKT1360866</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Abhisekh chhetri</t>
+          <t>Krishna Sagar Shahi</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -10383,12 +10906,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -10398,44 +10921,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:30:38 AM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>08 Oct 2026 12:53:09 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 29m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1363012</t>
+          <t>TKT1361710</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Pratik Raj Amatya</t>
+          <t>Abhisekh chhetri</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10465,22 +10988,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:14:14 AM</t>
+          <t>07 Oct 2026 11:30:38 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -10490,19 +11013,19 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>1d 1h 29m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1360491</t>
+          <t>TKT1363012</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Tirtha Kumari Limbu</t>
+          <t>Pratik Raj Amatya</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -10527,27 +11050,27 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:06:26 PM</t>
+          <t>08 Oct 2026 10:14:14 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -10557,74 +11080,74 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 36m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1363347</t>
+          <t>TKT1360491</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Tirtha Kumari Limbu</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>06 Oct 2026 12:06:26 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:26:02 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>2d 1h 36m</t>
         </is>
       </c>
     </row>
@@ -10661,37 +11184,171 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
           <t>Case : stb issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Case : stb issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:16:26 PM</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:16:26 PM</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:26:02 PM</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360585</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:27:53 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:00:36 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:59:40 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 31m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>2d 59m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9001,10 +9001,8 @@
           <t>Suresh maharjan</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9841213338</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9841213338</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9072,10 +9070,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH48" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH48" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
@@ -9094,10 +9090,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
@@ -9108,32 +9102,438 @@
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 31m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 59m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 31m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>2d 59m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>5g not showing</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361754</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9860256413</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:06:45 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9860256413</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:00:46 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:06:22 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Bright Future Sec. School - School M7Q8+6H6 Kalankisthan Rd Chandragiri 44600 - Kathmandu Metropolit</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>12:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:05 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>5g not showing</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361754</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9860256413</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:06:45 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9860256413</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:00:46 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:06:22 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Bright Future Sec. School - School M7Q8+6H6 Kalankisthan Rd Chandragiri 44600 - Kathmandu Metropolit</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>12:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9185,7 +9585,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9195,7 +9595,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -9206,7 +9606,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9618,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 47m</t>
+          <t>21h 6m</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9630,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 14h 7m</t>
+          <t>2d 11h 27m</t>
         </is>
       </c>
     </row>
@@ -9289,14 +9689,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -9434,41 +9834,41 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -9480,14 +9880,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -9498,12 +9898,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -9526,14 +9926,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -9549,14 +9949,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -9567,19 +9967,19 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -9588,181 +9988,137 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1359234</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ram Sharan Khatri</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -9782,22 +10138,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -9807,29 +10163,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 22m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -9849,22 +10205,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -9874,19 +10230,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9916,22 +10272,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -9941,39 +10297,39 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1361092</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Siddhartha Raut</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -9983,32 +10339,32 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>
@@ -10082,22 +10438,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -10117,32 +10473,32 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
@@ -10216,32 +10572,32 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1359155</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Ranjita Pandey</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -10251,44 +10607,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:21:29 AM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 23h 15m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1360911</t>
+          <t>TKT1359155</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Abishek Chaudhary</t>
+          <t>Ranjita Pandey</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10318,22 +10674,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:07:29 PM</t>
+          <t>05 Oct 2026 11:21:29 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -10343,19 +10699,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 7m</t>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1360598</t>
+          <t>TKT1360911</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Abishek Chaudhary</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -10385,22 +10741,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:10:30 PM</t>
+          <t>06 Oct 2026 04:07:29 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10410,19 +10766,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>1d 19h 7m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1355352</t>
+          <t>TKT1360598</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Parkas Nepal</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10437,12 +10793,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -10452,32 +10808,32 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:50:53 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:03:59 PM</t>
+          <t>06 Oct 2026 01:10:30 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:37:09 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2d 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>5d 21h 33m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
@@ -10551,22 +10907,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1358019</t>
+          <t>TKT1355352</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Parkas Nepal</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -10586,64 +10942,64 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:26:23 PM</t>
+          <t>06 Oct 2026 10:50:53 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 01:58:13 PM</t>
+          <t>02 Oct 2026 02:03:59 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:55:15 AM</t>
+          <t>08 Oct 2026 11:37:09 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 28m</t>
+          <t>2d 46m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 57m</t>
+          <t>5d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1360253</t>
+          <t>TKT1358019</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Ajay Kumar Chaudhary</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -10653,44 +11009,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>04 Oct 2026 02:26:23 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 09:42:25 AM</t>
+          <t>04 Oct 2026 01:58:13 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>08 Oct 2026 11:55:15 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 21h 28m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 20m</t>
+          <t>3d 21h 57m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1360955</t>
+          <t>TKT1360253</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GAURAV KOIRALA</t>
+          <t>Ajay Kumar Chaudhary</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10720,22 +11076,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:36:08 PM</t>
+          <t>06 Oct 2026 09:42:25 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -10745,19 +11101,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 52m</t>
+          <t>2d 2h 20m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1355547</t>
+          <t>TKT1360955</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kishan Jaisawal</t>
+          <t>GAURAV KOIRALA</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -10787,22 +11143,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:52:51 PM</t>
+          <t>06 Oct 2026 04:36:08 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -10812,19 +11168,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 33m</t>
+          <t>1d 19h 52m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1360866</t>
+          <t>TKT1355547</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Krishna Sagar Shahi</t>
+          <t>Kishan Jaisawal</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10839,12 +11195,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -10854,32 +11210,32 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>02 Oct 2026 03:52:51 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:53:09 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>5d 20h 33m</t>
         </is>
       </c>
     </row>
@@ -10953,12 +11309,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1361710</t>
+          <t>TKT1360866</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Abhisekh chhetri</t>
+          <t>Krishna Sagar Shahi</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10973,12 +11329,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -10988,44 +11344,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:30:38 AM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>08 Oct 2026 12:53:09 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 29m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1363012</t>
+          <t>TKT1361710</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Pratik Raj Amatya</t>
+          <t>Abhisekh chhetri</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -11055,22 +11411,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:14:14 AM</t>
+          <t>07 Oct 2026 11:30:38 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -11080,19 +11436,19 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>1d 1h 29m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1360491</t>
+          <t>TKT1363012</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Tirtha Kumari Limbu</t>
+          <t>Pratik Raj Amatya</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -11122,22 +11478,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:06:26 PM</t>
+          <t>08 Oct 2026 10:14:14 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -11147,39 +11503,39 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 36m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1363347</t>
+          <t>TKT1360491</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Tirtha Kumari Limbu</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -11189,32 +11545,32 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>06 Oct 2026 12:06:26 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:26:02 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>2d 1h 36m</t>
         </is>
       </c>
     </row>
@@ -11288,67 +11644,268 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>TKT1363347</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:16:26 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:26:02 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
           <t>TKT1360585</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Suresh maharjan</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 02:27:53 PM</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 01:00:36 PM</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 01:59:40 PM</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>1d 23h 31m</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>2d 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361754</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:06:45 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:00:46 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:06:22 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361754</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Saroj khanal</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:06:45 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:00:46 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:06:22 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9198,10 +9198,8 @@
           <t>Saroj khanal</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9860256413</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9860256413</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9269,10 +9267,8 @@
           <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
-      <c r="AH49" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH49" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
@@ -9291,10 +9287,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -9305,7 +9299,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9401,10 +9395,8 @@
           <t>Saroj khanal</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9860256413</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9860256413</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9472,10 +9464,8 @@
           <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
-      <c r="AH50" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH50" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
@@ -9494,10 +9484,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -9508,32 +9496,231 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>1d 59m</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 5m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:16 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 ayena</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356638</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing lama</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing lama</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9704026916</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:16:58 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>CHB9704026916</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:40:15 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:16:58 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>New Himalayan Sherpa Kitchen New Himalayan Sherpa Kitchen - Restaurant P9H7+GHQ Ramhiti, Road 44600,</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>Tseringnyimathokra@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr"/>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L39-8</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>4d 23h 36m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9744,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9585,7 +9772,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9606,7 +9793,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -9689,14 +9876,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -9861,14 +10048,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>16</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11995,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -11875,7 +12062,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9592,10 +9592,8 @@
           <t>Tenzing lama</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9704026916</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9704026916</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -9681,10 +9679,8 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -9695,7 +9691,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9720,6 +9720,217 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:45 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359624</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Buddhi Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Buddhi Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9841710489</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:45:43 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9841710489</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:21:27 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:45:43 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.672137</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Near Mahakali Oil Store ,Araniko Highway, Suryabinayak Madhyapur Thimi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>thapabuddibahadur@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>04:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L17-3</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.399734</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 24m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9731,7 +9942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9740,7 +9951,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9768,7 +9979,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -9778,7 +9989,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -9789,7 +10000,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -9801,7 +10012,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21h 6m</t>
+          <t>20h 20m</t>
         </is>
       </c>
     </row>
@@ -9813,7 +10024,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 27m</t>
+          <t>2d 11h 50m</t>
         </is>
       </c>
     </row>
@@ -9872,14 +10083,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -10044,14 +10255,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -12092,6 +12303,73 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359624</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Buddhi Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:45:43 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:21:27 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:45:43 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>2d 22h 24m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9787,10 +9787,8 @@
           <t>Buddhi Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9841710489</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9841710489</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -9825,10 +9823,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.672137</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.672137</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -9884,25 +9880,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L17-3</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.399734</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.399734</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -9951,7 +9943,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12336,7 +12328,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -9923,6 +9923,1455 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359411</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9848447759</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848447759</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:11:21 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Panga Kirtipur 44600, Kalanki - Kathmandu Metropolitan, Kathmandu, Bagmati, Nepal, Nepal, Kathmandu</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>9848447759@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>07:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>CDB106</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359411</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9848447759</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848447759</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:11:21 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Panga Kirtipur 44600, Kalanki - Kathmandu Metropolitan, Kathmandu, Bagmati, Nepal, Nepal, Kathmandu</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>9848447759@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>07:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>CDB106</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357911</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Nilisha Acharya</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Nilisha Acharya</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9848938626</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:21:42 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9848938626</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:14:17 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:09:43 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Aarambha Family Fast Food Restaurant - Restaurant Mahantar Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>acharyanilisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr"/>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L43-4</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>1d 48m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 55m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 ayena</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356638</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing lama</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing lama</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9704026916</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:16:58 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>CHB9704026916</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:40:15 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:43 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr"/>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>New Himalayan Sherpa Kitchen New Himalayan Sherpa Kitchen - Restaurant P9H7+GHQ Ramhiti, Road 44600,</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>Tseringnyimathokra@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>16:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr"/>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L39-8</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr"/>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>5d 28m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:08 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361765</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9851019499</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:28:20 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9851019499</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:06:18 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:10 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.68909</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Near Pokhrel Kirana Store, Chandragiri, balambu,kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>nirmalghimiregulmi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>13:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB069</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.24699</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 39m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 1m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361765</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9851019499</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:28:20 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9851019499</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:06:18 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:10 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.68909</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Near Pokhrel Kirana Store, Chandragiri, balambu,kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>nirmalghimiregulmi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>13:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB069</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.24699</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 39m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 1m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360561</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Rina Pandey</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Rina Pandey</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9841310587</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:47:17 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9851142284</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:47:17 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:39:45 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.688379</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>M7QC+HH9,Kathmandu Chandragiri 44600 Near by Sundarban School Of Science, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>magargrinesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>21:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.270062</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9934,7 +11383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9943,7 +11392,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9971,7 +11420,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -9981,7 +11430,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9992,7 +11441,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -10004,7 +11453,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 20m</t>
+          <t>1d 8m</t>
         </is>
       </c>
     </row>
@@ -10016,7 +11465,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 50m</t>
+          <t>2d 12h 11m</t>
         </is>
       </c>
     </row>
@@ -10075,14 +11524,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -10093,10 +11542,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -10247,14 +11696,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -10293,10 +11742,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -12362,6 +13811,408 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359411</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:11:21 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359411</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Chhetra Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:48:56 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:11:21 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>3d 1h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356638</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing lama</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:16:58 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:40:15 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:43 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>5d 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361765</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:28:20 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:06:18 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:10 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 39m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361765</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Ghimire</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:28:20 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:06:18 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:08:10 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 39m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360561</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Rina Pandey</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:47:17 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:47:17 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:39:45 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW59"/>
+  <dimension ref="A1:AW61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9990,10 +9990,8 @@
           <t>Chhetra Bahadur Budhathoki</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9848447759</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9848447759</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10083,10 +10081,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -10097,7 +10093,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10193,10 +10189,8 @@
           <t>Chhetra Bahadur Budhathoki</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9848447759</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9848447759</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10286,10 +10280,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10300,7 +10292,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10396,10 +10388,8 @@
           <t>Nilisha Acharya</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9848938626</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9848938626</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10485,10 +10475,8 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -10499,7 +10487,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -10595,10 +10583,8 @@
           <t>Tenzing lama</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9704026916</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9704026916</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -10688,10 +10674,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
@@ -10702,7 +10686,7 @@
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -10798,10 +10782,8 @@
           <t>Nirmal Ghimire</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9851019499</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9851019499</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -10836,10 +10818,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.68909</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.68909</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -10877,10 +10857,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH57" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH57" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
@@ -10899,25 +10877,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB069</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.24699</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.24699</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -11013,10 +10987,8 @@
           <t>Nirmal Ghimire</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9851019499</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9851019499</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11051,10 +11023,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.68909</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.68909</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -11092,10 +11062,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH58" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH58" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
@@ -11114,25 +11082,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>CDB069</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.24699</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.24699</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11228,10 +11192,8 @@
           <t>Rina Pandey</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9841310587</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9841310587</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11266,10 +11228,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.688379</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.688379</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11325,50 +11285,252 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.270062</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.270062</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS59" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 52m</t>
-        </is>
-      </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 52m</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV59" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:20 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr"/>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" s="3" t="inlineStr"/>
+      <c r="W60" s="3" t="inlineStr"/>
+      <c r="X60" s="3" t="inlineStr"/>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr"/>
+      <c r="AA60" s="3" t="inlineStr"/>
+      <c r="AB60" s="3" t="inlineStr"/>
+      <c r="AC60" s="3" t="inlineStr"/>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr"/>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr"/>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr"/>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr"/>
+      <c r="AM60" s="3" t="inlineStr"/>
+      <c r="AN60" s="3" t="inlineStr"/>
+      <c r="AO60" s="3" t="inlineStr"/>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr"/>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr"/>
+      <c r="V61" s="3" t="inlineStr"/>
+      <c r="W61" s="3" t="inlineStr"/>
+      <c r="X61" s="3" t="inlineStr"/>
+      <c r="Y61" s="3" t="inlineStr"/>
+      <c r="Z61" s="3" t="inlineStr"/>
+      <c r="AA61" s="3" t="inlineStr"/>
+      <c r="AB61" s="3" t="inlineStr"/>
+      <c r="AC61" s="3" t="inlineStr"/>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr"/>
+      <c r="AF61" s="3" t="inlineStr"/>
+      <c r="AG61" s="3" t="inlineStr"/>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr"/>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr"/>
+      <c r="AM61" s="3" t="inlineStr"/>
+      <c r="AN61" s="3" t="inlineStr"/>
+      <c r="AO61" s="3" t="inlineStr"/>
+      <c r="AP61" s="3" t="inlineStr"/>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11554,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11420,7 +11582,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -11441,7 +11603,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -13844,7 +14006,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -13911,7 +14073,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -13978,7 +14140,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -14045,7 +14207,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -14112,7 +14274,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -14179,7 +14341,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW61"/>
+  <dimension ref="A1:AW62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11534,6 +11534,109 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:31 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr"/>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr"/>
+      <c r="V62" s="3" t="inlineStr"/>
+      <c r="W62" s="3" t="inlineStr"/>
+      <c r="X62" s="3" t="inlineStr"/>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="inlineStr"/>
+      <c r="AA62" s="3" t="inlineStr"/>
+      <c r="AB62" s="3" t="inlineStr"/>
+      <c r="AC62" s="3" t="inlineStr"/>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr"/>
+      <c r="AF62" s="3" t="inlineStr"/>
+      <c r="AG62" s="3" t="inlineStr"/>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr"/>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr"/>
+      <c r="AM62" s="3" t="inlineStr"/>
+      <c r="AN62" s="3" t="inlineStr"/>
+      <c r="AO62" s="3" t="inlineStr"/>
+      <c r="AP62" s="3" t="inlineStr"/>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11582,7 +11685,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -11603,7 +11706,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW62"/>
+  <dimension ref="A1:AW66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11637,6 +11637,854 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 4:11 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362572</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Babu Khadka</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Babu Khadka</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9860103708</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:11:37 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9860103708</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 07:28:15 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:11:37 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>27.6648</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>M978+R4C, Anantalingeshwar,Near by Balkot ward no 2 Office, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>niyankhadka.nk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>06:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>85.365598</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363235</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Man Shrestha</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Man Shrestha</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9861234529</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:18:05 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9861234529</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:18:05 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:00:43 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.68607</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Near to Santosh Hair cutting , Satungal , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>shresthajason5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>03:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.25034</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:50 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359908</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9847863055</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9848260073</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:50:42 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>27.67087</t>
+        </is>
+      </c>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Near Panga Dobato Bus Stop Panga Rd, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>gamechrone86@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>01:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>85.28472</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 3:49 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359908</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9847863055</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>9848260073</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:50:42 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr">
+        <is>
+          <t>27.67087</t>
+        </is>
+      </c>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Near Panga Dobato Bus Stop Panga Rd, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>gamechrone86@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>01:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>85.28472</t>
+        </is>
+      </c>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11648,7 +12496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11657,7 +12505,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11685,7 +12533,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -11695,7 +12543,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -11706,7 +12554,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -11718,7 +12566,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 8m</t>
+          <t>1d 1h 15m</t>
         </is>
       </c>
     </row>
@@ -11730,7 +12578,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 12h 11m</t>
+          <t>2d 10h 4m</t>
         </is>
       </c>
     </row>
@@ -11789,14 +12637,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -11961,14 +12809,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -14478,6 +15326,274 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362572</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Babu Khadka</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:11:37 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 07:28:15 PM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:11:37 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363235</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Ganesh Man Shrestha</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:18:05 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:18:05 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:00:43 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359908</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:50:42 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359908</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Prashant Gharti Magar</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:43 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:50:42 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW66"/>
+  <dimension ref="A1:AW68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11704,10 +11704,8 @@
           <t>Nirajan Babu Khadka</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9860103708</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9860103708</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -11742,10 +11740,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y63" s="3" t="inlineStr">
-        <is>
-          <t>27.6648</t>
-        </is>
+      <c r="Y63" s="3" t="n">
+        <v>27.6648</v>
       </c>
       <c r="Z63" s="3" t="inlineStr">
         <is>
@@ -11801,25 +11797,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>85.365598</t>
-        </is>
+      <c r="AP63" s="3" t="n">
+        <v>85.36559800000001</v>
       </c>
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -11915,10 +11907,8 @@
           <t>Ganesh Man Shrestha</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9861234529</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9861234529</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -11953,10 +11943,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.68607</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.68607</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -11994,10 +11982,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH64" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH64" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI64" s="3" t="inlineStr">
         <is>
@@ -12016,25 +12002,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>CDB206</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.25034</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.25033999999999</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -12130,10 +12112,8 @@
           <t>Prashant Gharti Magar</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9847863055</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9847863055</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -12168,10 +12148,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y65" s="3" t="inlineStr">
-        <is>
-          <t>27.67087</t>
-        </is>
+      <c r="Y65" s="3" t="n">
+        <v>27.67087</v>
       </c>
       <c r="Z65" s="3" t="inlineStr">
         <is>
@@ -12227,25 +12205,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP65" s="3" t="inlineStr">
-        <is>
-          <t>85.28472</t>
-        </is>
+      <c r="AP65" s="3" t="n">
+        <v>85.28471999999999</v>
       </c>
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
@@ -12341,10 +12315,8 @@
           <t>Prashant Gharti Magar</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9847863055</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9847863055</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -12379,10 +12351,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y66" s="3" t="inlineStr">
-        <is>
-          <t>27.67087</t>
-        </is>
+      <c r="Y66" s="3" t="n">
+        <v>27.67087</v>
       </c>
       <c r="Z66" s="3" t="inlineStr">
         <is>
@@ -12438,48 +12408,466 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP66" s="3" t="inlineStr">
-        <is>
-          <t>85.28472</t>
-        </is>
+      <c r="AP66" s="3" t="n">
+        <v>85.28471999999999</v>
       </c>
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 40m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS66" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 40m</t>
-        </is>
-      </c>
-      <c r="AT66" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 40m</t>
-        </is>
-      </c>
-      <c r="AU66" s="3" t="inlineStr">
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 4:22 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363469</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Sunney Sharma</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Sunney Sharma</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9841540836</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:22:22 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9861806230</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:57:34 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:22:22 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.664262</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>near by The Bamboo Cottage &amp; Sekuwa Station - Restaurant, Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>sharma.sunney21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr"/>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>01:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>CDB498</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.335362</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV66" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW66" s="3" t="inlineStr">
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362992</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Punam Prajapati</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Punam Prajapati</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9849161665</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:54 AM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9849161665</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:54 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:28:34 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.6874</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>Krisipidi,Backside of Buddisht Temple,Chandragiri-5,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>punamprajapati70@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>06:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>CDB435</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.2384</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -12496,7 +12884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12533,7 +12921,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -12543,7 +12931,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -12554,7 +12942,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12954,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 15m</t>
+          <t>1d 9m</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12966,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 10h 4m</t>
+          <t>2d 7h 21m</t>
         </is>
       </c>
     </row>
@@ -12637,14 +13025,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -12809,14 +13197,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15747,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -15426,7 +15814,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -15493,7 +15881,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -15560,14 +15948,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>05 Oct 2026 08:09:43 PM</t>
@@ -15591,6 +15979,140 @@
       <c r="M69" s="5" t="inlineStr">
         <is>
           <t>2d 19h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363469</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Sunney Sharma</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:22:22 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:57:34 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:22:22 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362992</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Punam Prajapati</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:54 AM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:03:54 AM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:28:34 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW68"/>
+  <dimension ref="A1:AW69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12518,10 +12518,8 @@
           <t>Sunney Sharma</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9841540836</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9841540836</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -12556,10 +12554,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.664262</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.664262</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -12615,25 +12611,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>CDB498</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.335362</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.335362</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
@@ -12729,10 +12721,8 @@
           <t>Punam Prajapati</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9849161665</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9849161665</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -12767,10 +12757,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y68" s="3" t="inlineStr">
-        <is>
-          <t>27.6874</t>
-        </is>
+      <c r="Y68" s="3" t="n">
+        <v>27.6874</v>
       </c>
       <c r="Z68" s="3" t="inlineStr">
         <is>
@@ -12826,50 +12814,249 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>CDB435</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.2384</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.2384</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS68" s="3" t="inlineStr">
-        <is>
-          <t>6h 24m</t>
-        </is>
-      </c>
-      <c r="AT68" s="3" t="inlineStr">
-        <is>
-          <t>6h 24m</t>
-        </is>
-      </c>
-      <c r="AU68" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV68" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW68" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357638</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Hari Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Hari Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9745942422</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:39:53 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>LTP9745942422</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:57:58 AM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:39:53 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr"/>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>Shanta bhawan Shanta bhawan - Bicycle store M8J4+36M ????? ??? Lalitpur 44600, Lalitpur, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>9745942422@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>12:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>CDB222</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr"/>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>4d 5h 41m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -12884,12 +13071,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -12921,7 +13108,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -12931,7 +13118,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -12942,7 +13129,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -12954,7 +13141,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 9m</t>
+          <t>23h 33m</t>
         </is>
       </c>
     </row>
@@ -12966,7 +13153,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 7h 21m</t>
+          <t>2d 8h 29m</t>
         </is>
       </c>
     </row>
@@ -13007,14 +13194,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -13151,14 +13338,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16202,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -16082,14 +16269,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>08 Oct 2026 10:03:54 AM</t>
@@ -16113,6 +16300,73 @@
       <c r="M71" s="5" t="inlineStr">
         <is>
           <t>6h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357638</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Hari Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:39:53 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:57:58 AM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:39:53 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>4d 5h 41m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW69"/>
+  <dimension ref="A1:AW70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12924,10 +12924,8 @@
           <t>Hari Bahadur Bhujel</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9745942422</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9745942422</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -13017,10 +13015,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
@@ -13031,32 +13027,135 @@
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>4d 5h 41m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
           <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS69" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT69" s="3" t="inlineStr">
-        <is>
-          <t>4d 5h 41m</t>
-        </is>
-      </c>
-      <c r="AU69" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV69" s="3" t="inlineStr">
-        <is>
-          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr"/>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr"/>
+      <c r="V70" s="3" t="inlineStr"/>
+      <c r="W70" s="3" t="inlineStr"/>
+      <c r="X70" s="3" t="inlineStr"/>
+      <c r="Y70" s="3" t="inlineStr"/>
+      <c r="Z70" s="3" t="inlineStr"/>
+      <c r="AA70" s="3" t="inlineStr"/>
+      <c r="AB70" s="3" t="inlineStr"/>
+      <c r="AC70" s="3" t="inlineStr"/>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr"/>
+      <c r="AF70" s="3" t="inlineStr"/>
+      <c r="AG70" s="3" t="inlineStr"/>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr"/>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr"/>
+      <c r="AM70" s="3" t="inlineStr"/>
+      <c r="AN70" s="3" t="inlineStr"/>
+      <c r="AO70" s="3" t="inlineStr"/>
+      <c r="AP70" s="3" t="inlineStr"/>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13179,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13108,7 +13207,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -13129,7 +13228,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16435,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW70"/>
+  <dimension ref="A1:AW73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13159,6 +13159,623 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358021</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Ishwor Shrestha</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Ishwor Shrestha</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9823640720</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:15:51 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9823640720</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:01:21 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:15:51 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.67636</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-3,Pulchwok,Backiside of Sumeru City Hospital, Near IMAGE TRADE LINK, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr">
+        <is>
+          <t>shresthaishwor46@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>13:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.31471</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>4d 3h 14m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 5:14 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360358</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9860021884</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9860021884</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:14:02 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr"/>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>D Moksha Mustang Thakali - Family restaurant P85J+HCX Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>subashbasnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>CDB491</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr"/>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 5:13 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360358</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9860021884</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9860021884</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:14:02 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>D Moksha Mustang Thakali - Family restaurant P85J+HCX Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>subashbasnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>CDB491</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr"/>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13170,7 +13787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13179,7 +13796,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13207,7 +13824,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -13217,7 +13834,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -13228,7 +13845,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13857,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23h 33m</t>
+          <t>1d 26m</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13869,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 8h 29m</t>
+          <t>2d 9h 22m</t>
         </is>
       </c>
     </row>
@@ -13311,14 +13928,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -13483,14 +14100,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -16469,6 +17086,207 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358021</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Ishwor Shrestha</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:15:51 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:01:21 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:15:51 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>4d 3h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360358</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:14:02 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360358</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:14:02 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13226,10 +13226,8 @@
           <t>Ishwor Shrestha</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9823640720</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9823640720</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -13264,10 +13262,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.67636</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.67636</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -13323,25 +13319,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.31471</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.31471000000001</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -13437,10 +13429,8 @@
           <t>Khel Bahadur Basnet</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9860021884</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9860021884</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -13530,10 +13520,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
@@ -13544,7 +13532,7 @@
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
@@ -13640,10 +13628,8 @@
           <t>Khel Bahadur Basnet</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9860021884</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9860021884</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -13733,10 +13719,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
@@ -13747,7 +13731,7 @@
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
@@ -13796,7 +13780,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17119,7 +17103,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -17186,7 +17170,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -17253,7 +17237,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW73"/>
+  <dimension ref="A1:AW74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13760,6 +13760,221 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 5:41 PM</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361265</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Utsav Panthi</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Utsav Panthi</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>9860922803</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:41:50 PM</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>9860922803</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:07:37 PM</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:41:50 PM</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>27.6476408</t>
+        </is>
+      </c>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA74" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>Elite sports trainning centre nakkhu dol, J8W5+RV9, Lalitpur 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF74" s="3" t="inlineStr">
+        <is>
+          <t>utsavpe@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG74" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH74" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI74" s="3" t="inlineStr">
+        <is>
+          <t>17:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AK74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>85.3103121</t>
+        </is>
+      </c>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 34m</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13771,7 +13986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13780,7 +13995,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13808,7 +14023,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -13818,7 +14033,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -13829,7 +14044,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>
@@ -13841,7 +14056,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 26m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
@@ -13853,7 +14068,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 9h 22m</t>
+          <t>2d 9h 5m</t>
         </is>
       </c>
     </row>
@@ -13930,10 +14145,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -14126,14 +14341,14 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -14144,19 +14359,19 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -14172,14 +14387,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -14195,14 +14410,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -14213,19 +14428,19 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -14234,181 +14449,137 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1353630</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Ranjana Yadav</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 10:10:10 AM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 09:10:39 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>6d 23h</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1359234</t>
+          <t>TKT1353630</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ram Sharan Khatri</t>
+          <t>Ranjana Yadav</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14428,22 +14599,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router uprade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:58:54 AM</t>
+          <t>01 Oct 2026 10:10:10 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:21:21 AM</t>
+          <t>08 Oct 2026 09:10:39 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -14453,29 +14624,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 22m</t>
+          <t>6d 23h</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1357447</t>
+          <t>TKT1359234</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Birendra Prasad Joshi</t>
+          <t>Ram Sharan Khatri</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -14495,22 +14666,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:36:39 AM</t>
+          <t>05 Oct 2026 11:58:54 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:18:19 AM</t>
+          <t>08 Oct 2026 09:21:21 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -14520,19 +14691,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>3d 23h 41m</t>
+          <t>2d 21h 22m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1361092</t>
+          <t>TKT1357447</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Raut</t>
+          <t>Birendra Prasad Joshi</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -14562,22 +14733,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:25:13 PM</t>
+          <t>04 Oct 2026 09:36:39 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:47:39 AM</t>
+          <t>08 Oct 2026 09:18:19 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -14587,39 +14758,39 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 22m</t>
+          <t>3d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1362893</t>
+          <t>TKT1361092</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sushila Shrestha</t>
+          <t>Siddhartha Raut</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -14629,32 +14800,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
+          <t>Case : 6g router khoi..  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:11:00 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 08:58:24 AM</t>
+          <t>06 Oct 2026 06:25:13 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:24:57 AM</t>
+          <t>08 Oct 2026 09:47:39 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1h 26m</t>
+          <t>1d 15h 22m</t>
         </is>
       </c>
     </row>
@@ -14728,22 +14899,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1357830</t>
+          <t>TKT1362893</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Gitaraj B.K</t>
+          <t>Sushila Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -14763,32 +14934,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>Case : remote damage  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:17 PM</t>
+          <t>08 Oct 2026 09:11:00 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:29:40 PM</t>
+          <t>08 Oct 2026 08:58:24 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:44:17 AM</t>
+          <t>08 Oct 2026 10:24:57 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 7m</t>
+          <t>1h 13m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 14m</t>
+          <t>1h 26m</t>
         </is>
       </c>
     </row>
@@ -14862,32 +15033,32 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1359155</t>
+          <t>TKT1357830</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Ranjita Pandey</t>
+          <t>Gitaraj B.K</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -14897,44 +15068,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>04 Oct 2026 12:37:17 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 11:21:29 AM</t>
+          <t>04 Oct 2026 12:29:40 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:36:48 AM</t>
+          <t>08 Oct 2026 10:44:17 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 22h 7m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 15m</t>
+          <t>3d 22h 14m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1360911</t>
+          <t>TKT1359155</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Abishek Chaudhary</t>
+          <t>Ranjita Pandey</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -14964,22 +15135,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:07:29 PM</t>
+          <t>05 Oct 2026 11:21:29 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:14:37 AM</t>
+          <t>08 Oct 2026 10:36:48 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -14989,19 +15160,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 7m</t>
+          <t>2d 23h 15m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1360598</t>
+          <t>TKT1360911</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Abishek Chaudhary</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -15031,22 +15202,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Upgrade WIFI6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:10:30 PM</t>
+          <t>06 Oct 2026 04:07:29 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:16:25 AM</t>
+          <t>08 Oct 2026 11:14:37 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -15056,19 +15227,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>1d 19h 7m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1355352</t>
+          <t>TKT1360598</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Parkas Nepal</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -15083,12 +15254,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -15098,32 +15269,32 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:50:53 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:03:59 PM</t>
+          <t>06 Oct 2026 01:10:30 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:37:09 AM</t>
+          <t>08 Oct 2026 11:16:25 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2d 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>5d 21h 33m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
@@ -15197,22 +15368,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1358019</t>
+          <t>TKT1355352</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Parkas Nepal</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -15232,64 +15403,64 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:26:23 PM</t>
+          <t>06 Oct 2026 10:50:53 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 01:58:13 PM</t>
+          <t>02 Oct 2026 02:03:59 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:55:15 AM</t>
+          <t>08 Oct 2026 11:37:09 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 28m</t>
+          <t>2d 46m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 57m</t>
+          <t>5d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1360253</t>
+          <t>TKT1358019</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Ajay Kumar Chaudhary</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -15299,44 +15470,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Setup box  auto off   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>04 Oct 2026 02:26:23 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 09:42:25 AM</t>
+          <t>04 Oct 2026 01:58:13 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:02:38 PM</t>
+          <t>08 Oct 2026 11:55:15 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 21h 28m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 20m</t>
+          <t>3d 21h 57m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1360955</t>
+          <t>TKT1360253</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>GAURAV KOIRALA</t>
+          <t>Ajay Kumar Chaudhary</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -15366,22 +15537,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:36:08 PM</t>
+          <t>06 Oct 2026 09:42:25 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:28:41 PM</t>
+          <t>08 Oct 2026 12:02:38 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -15391,19 +15562,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 52m</t>
+          <t>2d 2h 20m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1355547</t>
+          <t>TKT1360955</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Kishan Jaisawal</t>
+          <t>GAURAV KOIRALA</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -15433,22 +15604,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:52:51 PM</t>
+          <t>06 Oct 2026 04:36:08 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:26:32 PM</t>
+          <t>08 Oct 2026 12:28:41 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -15458,19 +15629,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 33m</t>
+          <t>1d 19h 52m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1360866</t>
+          <t>TKT1355547</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Krishna Sagar Shahi</t>
+          <t>Kishan Jaisawal</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -15485,12 +15656,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -15500,32 +15671,32 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi -6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 03:46:11 PM</t>
+          <t>02 Oct 2026 03:52:51 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:53:09 PM</t>
+          <t>08 Oct 2026 12:26:32 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 6m</t>
+          <t>5d 20h 33m</t>
         </is>
       </c>
     </row>
@@ -15599,12 +15770,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1361710</t>
+          <t>TKT1360866</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Abhisekh chhetri</t>
+          <t>Krishna Sagar Shahi</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -15619,12 +15790,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -15634,44 +15805,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
+          <t>Case : wifi 6 router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:30:38 AM</t>
+          <t>06 Oct 2026 03:46:11 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:08 PM</t>
+          <t>08 Oct 2026 12:53:09 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 29m</t>
+          <t>1d 21h 6m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1363012</t>
+          <t>TKT1361710</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Pratik Raj Amatya</t>
+          <t>Abhisekh chhetri</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -15701,22 +15872,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 Router   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:14:14 AM</t>
+          <t>07 Oct 2026 11:30:38 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:30:36 PM</t>
+          <t>08 Oct 2026 01:00:08 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -15726,19 +15897,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>1d 1h 29m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1360491</t>
+          <t>TKT1363012</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Tirtha Kumari Limbu</t>
+          <t>Pratik Raj Amatya</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -15768,22 +15939,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:06:26 PM</t>
+          <t>08 Oct 2026 10:14:14 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:42:30 PM</t>
+          <t>08 Oct 2026 01:30:36 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -15793,39 +15964,39 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 36m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1363347</t>
+          <t>TKT1360491</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Tirtha Kumari Limbu</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -15835,32 +16006,32 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:16:26 PM</t>
+          <t>06 Oct 2026 12:06:26 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:26:02 PM</t>
+          <t>08 Oct 2026 01:42:30 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>2d 1h 36m</t>
         </is>
       </c>
     </row>
@@ -15934,12 +16105,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1360585</t>
+          <t>TKT1363347</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Suresh maharjan</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -15949,17 +16120,17 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -15969,64 +16140,64 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
+          <t>Case : stb issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:27:53 PM</t>
+          <t>08 Oct 2026 01:16:26 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 01:00:36 PM</t>
+          <t>08 Oct 2026 01:16:26 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:59:40 PM</t>
+          <t>08 Oct 2026 01:26:02 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 31m</t>
+          <t>9m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>2d 59m</t>
+          <t>9m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1361754</t>
+          <t>TKT1360585</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Saroj khanal</t>
+          <t>Suresh maharjan</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Change SSID / Wi-Fi Password</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -16036,32 +16207,32 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
+          <t>Case : Iptv issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:06:45 PM</t>
+          <t>06 Oct 2026 02:27:53 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 12:00:46 PM</t>
+          <t>06 Oct 2026 01:00:36 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:06:22 PM</t>
+          <t>08 Oct 2026 01:59:40 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>1d 59m</t>
+          <t>1d 23h 31m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 5m</t>
+          <t>2d 59m</t>
         </is>
       </c>
     </row>
@@ -16135,12 +16306,12 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1359624</t>
+          <t>TKT1361754</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Buddhi Bahadur Thapa</t>
+          <t>Saroj khanal</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -16150,17 +16321,17 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -16170,44 +16341,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : 5g not showing     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:45:43 PM</t>
+          <t>07 Oct 2026 01:06:45 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:21:27 PM</t>
+          <t>07 Oct 2026 12:00:46 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:45:43 PM</t>
+          <t>08 Oct 2026 02:06:22 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 59m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 24m</t>
+          <t>1d 2h 5m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1359411</t>
+          <t>TKT1359624</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Chhetra Bahadur Budhathoki</t>
+          <t>Buddhi Bahadur Thapa</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -16222,12 +16393,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -16237,32 +16408,32 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 01:48:56 PM</t>
+          <t>08 Oct 2026 02:45:43 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 01:48:56 PM</t>
+          <t>05 Oct 2026 04:21:27 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:11:21 PM</t>
+          <t>08 Oct 2026 02:45:43 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 22m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 22m</t>
+          <t>2d 22h 24m</t>
         </is>
       </c>
     </row>
@@ -16336,12 +16507,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1356638</t>
+          <t>TKT1359411</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Tenzing lama</t>
+          <t>Chhetra Bahadur Budhathoki</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -16371,54 +16542,54 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:16:58 PM</t>
+          <t>05 Oct 2026 01:48:56 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:40:15 PM</t>
+          <t>05 Oct 2026 01:48:56 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:08:43 PM</t>
+          <t>08 Oct 2026 03:11:21 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>51m</t>
+          <t>3d 1h 22m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>5d 28m</t>
+          <t>3d 1h 22m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1361765</t>
+          <t>TKT1356638</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Nirmal Ghimire</t>
+          <t>Tenzing lama</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16438,32 +16609,32 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 ayena  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 12:28:20 PM</t>
+          <t>08 Oct 2026 02:16:58 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 12:06:18 PM</t>
+          <t>03 Oct 2026 02:40:15 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:08:10 PM</t>
+          <t>08 Oct 2026 03:08:43 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 39m</t>
+          <t>51m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 1m</t>
+          <t>5d 28m</t>
         </is>
       </c>
     </row>
@@ -16537,22 +16708,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1360561</t>
+          <t>TKT1361765</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Rina Pandey</t>
+          <t>Nirmal Ghimire</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16572,44 +16743,44 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:47:17 PM</t>
+          <t>07 Oct 2026 12:28:20 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:47:17 PM</t>
+          <t>07 Oct 2026 12:06:18 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:39:45 PM</t>
+          <t>08 Oct 2026 03:08:10 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 52m</t>
+          <t>1d 2h 39m</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 52m</t>
+          <t>1d 3h 1m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1362572</t>
+          <t>TKT1360561</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Nirajan Babu Khadka</t>
+          <t>Rina Pandey</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -16624,12 +16795,12 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -16639,44 +16810,44 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:11:37 PM</t>
+          <t>06 Oct 2026 12:47:17 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 07:28:15 PM</t>
+          <t>06 Oct 2026 12:47:17 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:11:37 PM</t>
+          <t>08 Oct 2026 02:39:45 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 52m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>2d 1h 52m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1363235</t>
+          <t>TKT1362572</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Man Shrestha</t>
+          <t>Nirajan Babu Khadka</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -16691,12 +16862,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -16706,44 +16877,44 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:18:05 PM</t>
+          <t>08 Oct 2026 04:11:37 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:18:05 PM</t>
+          <t>07 Oct 2026 07:28:15 PM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:00:43 PM</t>
+          <t>08 Oct 2026 04:11:37 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>3h 42m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>3h 42m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1359908</t>
+          <t>TKT1363235</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Prashant Gharti Magar</t>
+          <t>Ganesh Man Shrestha</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -16758,12 +16929,12 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -16773,32 +16944,32 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:43 PM</t>
+          <t>08 Oct 2026 12:18:05 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:43 PM</t>
+          <t>08 Oct 2026 12:18:05 PM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:50:42 PM</t>
+          <t>08 Oct 2026 04:00:43 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2d 19h 40m</t>
+          <t>3h 42m</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2d 19h 40m</t>
+          <t>3h 42m</t>
         </is>
       </c>
     </row>
@@ -16872,12 +17043,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TKT1363469</t>
+          <t>TKT1359908</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Sunney Sharma</t>
+          <t>Prashant Gharti Magar</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -16907,44 +17078,44 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:22:22 PM</t>
+          <t>05 Oct 2026 08:09:43 PM</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 02:57:34 PM</t>
+          <t>05 Oct 2026 08:09:43 PM</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:22:22 PM</t>
+          <t>08 Oct 2026 03:50:42 PM</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 19h 40m</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1h 24m</t>
+          <t>2d 19h 40m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TKT1362992</t>
+          <t>TKT1363469</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Punam Prajapati</t>
+          <t>Sunney Sharma</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -16959,12 +17130,12 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -16974,64 +17145,64 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:03:54 AM</t>
+          <t>08 Oct 2026 04:22:22 PM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 10:03:54 AM</t>
+          <t>08 Oct 2026 02:57:34 PM</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:28:34 PM</t>
+          <t>08 Oct 2026 04:22:22 PM</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>6h 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>6h 24m</t>
+          <t>1h 24m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>TKT1357638</t>
+          <t>TKT1362992</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Hari Bahadur Bhujel</t>
+          <t>Punam Prajapati</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -17041,54 +17212,54 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:39:53 PM</t>
+          <t>08 Oct 2026 10:03:54 AM</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:57:58 AM</t>
+          <t>08 Oct 2026 10:03:54 AM</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:39:53 PM</t>
+          <t>08 Oct 2026 04:28:34 PM</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6h 24m</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>4d 5h 41m</t>
+          <t>6h 24m</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TKT1358021</t>
+          <t>TKT1357638</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Ishwor Shrestha</t>
+          <t>Hari Bahadur Bhujel</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17108,22 +17279,22 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : frequent disconnection  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 05:15:51 PM</t>
+          <t>08 Oct 2026 04:39:53 PM</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:01:21 PM</t>
+          <t>04 Oct 2026 10:57:58 AM</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 05:15:51 PM</t>
+          <t>08 Oct 2026 04:39:53 PM</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
@@ -17133,19 +17304,19 @@
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>4d 3h 14m</t>
+          <t>4d 5h 41m</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>TKT1360358</t>
+          <t>TKT1358021</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Khel Bahadur Basnet</t>
+          <t>Ishwor Shrestha</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -17160,12 +17331,12 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -17175,32 +17346,32 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:56 AM</t>
+          <t>08 Oct 2026 05:15:51 PM</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:56 AM</t>
+          <t>04 Oct 2026 02:01:21 PM</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 05:14:02 PM</t>
+          <t>08 Oct 2026 05:15:51 PM</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2d 6h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2d 6h 36m</t>
+          <t>4d 3h 14m</t>
         </is>
       </c>
     </row>
@@ -17268,6 +17439,140 @@
       <c r="M75" s="5" t="inlineStr">
         <is>
           <t>2d 6h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360358</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Khel Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:56 AM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:14:02 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361265</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Utsav Panthi</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:41:50 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:07:37 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:41:50 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h 34m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13827,10 +13827,8 @@
           <t>Utsav Panthi</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>9860922803</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>9860922803</v>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
@@ -13865,10 +13863,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y74" s="3" t="inlineStr">
-        <is>
-          <t>27.6476408</t>
-        </is>
+      <c r="Y74" s="3" t="n">
+        <v>27.6476408</v>
       </c>
       <c r="Z74" s="3" t="inlineStr">
         <is>
@@ -13906,10 +13902,8 @@
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH74" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH74" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI74" s="3" t="inlineStr">
         <is>
@@ -13928,25 +13922,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN74" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
           <t>4,7</t>
         </is>
       </c>
-      <c r="AP74" s="3" t="inlineStr">
-        <is>
-          <t>85.3103121</t>
-        </is>
+      <c r="AP74" s="3" t="n">
+        <v>85.3103121</v>
       </c>
       <c r="AQ74" s="3" t="inlineStr"/>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
@@ -13995,7 +13985,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17542,7 +17532,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW74"/>
+  <dimension ref="A1:AW75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13965,6 +13965,217 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 6:37 PM</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362096</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Aman Shakya</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Aman Shakya</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>9705477637</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:37:43 PM</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>9863833345</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:06:32 PM</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:37:43 PM</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>27.67482</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB75" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr">
+        <is>
+          <t>Balkumari (Inside Ring Road) https://www.google.com/maps/place/Kwako,+Lalitpur+44600/@27.674819,85.3</t>
+        </is>
+      </c>
+      <c r="AF75" s="3" t="inlineStr">
+        <is>
+          <t>amanshakya017@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG75" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH75" s="3" t="inlineStr"/>
+      <c r="AI75" s="3" t="inlineStr">
+        <is>
+          <t>13:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ75" s="3" t="inlineStr"/>
+      <c r="AK75" s="3" t="inlineStr"/>
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>CDB635</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>85.33319</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr"/>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 31m</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13976,7 +14187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13985,7 +14196,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14013,7 +14224,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -14023,7 +14234,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -14034,7 +14245,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.2%</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14257,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>23h 22m</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14269,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 9h 5m</t>
+          <t>2d 8h 26m</t>
         </is>
       </c>
     </row>
@@ -14117,14 +14328,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -14289,14 +14500,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -17566,6 +17777,73 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362096</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Aman Shakya</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:37:43 PM</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:06:32 PM</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:37:43 PM</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 31m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -14032,10 +14032,8 @@
           <t>Aman Shakya</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>9705477637</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>9705477637</v>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
@@ -14070,10 +14068,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y75" s="3" t="inlineStr">
-        <is>
-          <t>27.67482</t>
-        </is>
+      <c r="Y75" s="3" t="n">
+        <v>27.67482</v>
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
@@ -14129,25 +14125,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN75" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
           <t>CDB635</t>
         </is>
       </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>85.33319</t>
-        </is>
+      <c r="AP75" s="3" t="n">
+        <v>85.33319</v>
       </c>
       <c r="AQ75" s="3" t="inlineStr"/>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
@@ -14196,7 +14188,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17810,7 +17802,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW75"/>
+  <dimension ref="A1:AW76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -14168,6 +14168,213 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 8:42 PM</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360373</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:42:38 PM</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:48:28 AM</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:42:38 PM</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr"/>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA76" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB76" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF76" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG76" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH76" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI76" s="3" t="inlineStr">
+        <is>
+          <t>05:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ76" s="3" t="inlineStr"/>
+      <c r="AK76" s="3" t="inlineStr"/>
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO76" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr"/>
+      <c r="AQ76" s="3" t="inlineStr"/>
+      <c r="AR76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 54m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14179,7 +14386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -14188,7 +14395,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14216,7 +14423,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -14226,7 +14433,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -14237,7 +14444,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14456,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23h 22m</t>
+          <t>22h 52m</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14468,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 8h 26m</t>
+          <t>2d 8h 28m</t>
         </is>
       </c>
     </row>
@@ -14374,10 +14581,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -14653,10 +14860,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -17836,6 +18043,73 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360373</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:42:38 PM</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:48:28 AM</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 08:42:38 PM</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>2d 9h 54m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_08_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_08_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -14235,10 +14235,8 @@
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O76" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
@@ -14310,10 +14308,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH76" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH76" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI76" s="3" t="inlineStr">
         <is>
@@ -14332,10 +14328,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN76" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
@@ -14346,7 +14340,7 @@
       <c r="AQ76" s="3" t="inlineStr"/>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
@@ -14395,7 +14389,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -18076,7 +18070,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
